--- a/test2.xlsx
+++ b/test2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{25C7FDA3-0CEF-4244-B620-89A6E2648929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42A5AEA7-F23B-4633-9195-5B22DCC12618}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{25C7FDA3-0CEF-4244-B620-89A6E2648929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B03D5188-BC6B-4010-9ABF-D568041DE2E9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -331,6 +331,9 @@
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>10</v>
+      </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
